--- a/client/public/artefactos/ADI-09.xlsx
+++ b/client/public/artefactos/ADI-09.xlsx
@@ -271,7 +271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -455,11 +455,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -608,6 +641,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/client/public/artefactos/ADI-09.xlsx
+++ b/client/public/artefactos/ADI-09.xlsx
@@ -548,17 +548,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AppFabric_CachingServiceConfiguration BDFEDATARIO GestionCitasColas Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_casadelpensionista</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>AppFabric_CachingServiceConfiguration BDFEDATARIO BDPR11G2 GestionCitasColas Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_casadelpensionista</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Aporte, Asegurado/Afiliado, Beneficiario, Derecho previsional, Documento, Empleador/Aportante, Expediente/Trámite, Fiscalización, Inversión/FCR, Notificación, Pensión/Pensionista, Persona, Planilla, Prestación/Beneficio, Recaudación/Pago, Resolución, SCTR, Solicitud</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clientes, cotizaciones, pólizas y asegurados </t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
@@ -614,17 +626,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>BDPR19G8 BDPRAESC EMI18PRD EMI19PRD EMI20PRD IndicadoresONP NSP18PRD NSP19PRD NSP20PRD VisitasONP</t>
+          <t>BDPR11G4 BDPR19G8 BDPRAESC EMI18PRD EMI19PRD EMI20PRD IndicadoresONP NSP18PRD NSP19PRD NSP20PRD VisitasONP</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Aporte, Asegurado/Afiliado, Beneficiario, Derecho previsional, Documento, Empleador/Aportante, Expediente/Trámite, Fiscalización, Notificación, Pensión/Pensionista, Persona, Planilla, Prestación/Beneficio, Recaudación/Pago, Resolución, SCTR, Solicitud</t>
+          <t>Aporte, Asegurado/Afiliado, Beneficiario, Derecho previsional, Documento, Empleador/Aportante, Expediente/Trámite, Fiscalización, Inversión/FCR, Notificación, Pensión/Pensionista, Persona, Planilla, Prestación/Beneficio, Recaudación/Pago, Resolución, SCTR, Solicitud</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1156,12 +1168,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BDPR11G2 BDPR11G5 BDPR19G7 BDPR19G8 BDPRAESC BDPRD11G BDPRDCIA</t>
+          <t>BDPR11G2 BDPR11G4 BDPR11G5 BDPR19G7 BDPR19G8 BDPRAESC BDPRD11G BDPRDCIA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1181,7 +1193,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1480,12 +1492,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>AppFabric_CachingServiceConfiguration BDHOMESERVICE BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_Blogs WSS_Content_CentroDocumentos WSS_Content_CentroDocumentosConservert WSS_Content_CentroDocumentosPTE WSS_Content_Comites WSS_Content_Comunidades WSS_Content_Comunidades_DPR-OC WSS_Content_Comunidades_MDF WSS_Content_Conservert WSS_Content_Convocatorias_SQLOnly WSS_Content_DocumentosONP WSS_Content_DocumentosTAP WSS_Content_Evaluaciones_SQLOnly WSS_Content_Flujos WSS_Content_Hojavida WSS_Content_IntranetONP WSS_Content_IntranetTmp WSS_Content_MySiteONP WSS_Content_OTI WSS_Content_WorkFlows_SQLOnly WSS_Content_comunidades2</t>
+          <t>AppFabric_CachingServiceConfiguration BDHOMESERVICE BDPR11G2 BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_Blogs WSS_Content_CentroDocumentos WSS_Content_CentroDocumentosConservert WSS_Content_CentroDocumentosPTE WSS_Content_Comites WSS_Content_Comunidades WSS_Content_Comunidades_DPR-OC WSS_Content_Comunidades_MDF WSS_Content_Conservert WSS_Content_Convocatorias_SQLOnly WSS_Content_DocumentosONP WSS_Content_DocumentosTAP WSS_Content_Evaluaciones_SQLOnly WSS_Content_Flujos WSS_Content_Hojavida WSS_Content_IntranetONP WSS_Content_IntranetTmp WSS_Content_MySiteONP WSS_Content_OTI WSS_Content_WorkFlows_SQLOnly WSS_Content_comunidades2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1493,7 +1505,11 @@
           <t>Aporte, Asegurado/Afiliado, Beneficiario, Derecho previsional, Documento, Empleador/Aportante, Expediente/Trámite, Fiscalización, Inversión/FCR, Notificación, Pensión/Pensionista, Persona, Planilla, Prestación/Beneficio, Recaudación/Pago, Resolución, SCTR, Solicitud</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clientes, cotizaciones, pólizas y asegurados </t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>22</t>
@@ -1501,7 +1517,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">

--- a/client/public/artefactos/ADI-09.xlsx
+++ b/client/public/artefactos/ADI-09.xlsx
@@ -1492,12 +1492,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>AppFabric_CachingServiceConfiguration BDHOMESERVICE BDPR11G2 BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_Blogs WSS_Content_CentroDocumentos WSS_Content_CentroDocumentosConservert WSS_Content_CentroDocumentosPTE WSS_Content_Comites WSS_Content_Comunidades WSS_Content_Comunidades_DPR-OC WSS_Content_Comunidades_MDF WSS_Content_Conservert WSS_Content_Convocatorias_SQLOnly WSS_Content_DocumentosONP WSS_Content_DocumentosTAP WSS_Content_Evaluaciones_SQLOnly WSS_Content_Flujos WSS_Content_Hojavida WSS_Content_IntranetONP WSS_Content_IntranetTmp WSS_Content_MySiteONP WSS_Content_OTI WSS_Content_WorkFlows_SQLOnly WSS_Content_comunidades2</t>
+          <t>AppFabric_CachingServiceConfiguration BDHOMESERVICE BDPR11G2 BDPR11G4 BDPR19G8 Intranet_Search_Service_App_AnalyticsReportingStoreDB_f50686f013884112bfde419d3650cd0d Intranet_Search_Service_App_CrawlStoreDB_2bf206361c31431294ae6a6ddf3903b0 Intranet_Search_Service_App_DB_78606f633ea842da96d98d3834eb2d96 Intranet_Search_Service_App_LinksStoreDB_34895ae357f8471f99142dfa5de2e258 SIGA_1782 SIGA_55 SP2010_MMS_DB SP2010_UPS_ProfileDB SP2010_UPS_SocialDB SP2010_UPS_SyncDB SP2013_Config_DB SP2013_Logging_DB SP2013_MMS_DB SP2013_RS_DB SP2013_RS_DBTempDB SP2013_RS_DB_Alerting SP2013_SSApp_DB SP2013_SSApp_DB_AnalyticsReportingStore SP2013_SSApp_DB_CrawlStore SP2013_SSApp_DB_LinksStore SPSessionState_DB SharePoint_AdminContent_c5659f88-07fb-46cf-b613-b2b28ca85a7a StateService_b1089735c15a4b6890f51e09067fa0a2 WSS_Content_Blogs WSS_Content_CentroDocumentos WSS_Content_CentroDocumentosConservert WSS_Content_CentroDocumentosPTE WSS_Content_Comites WSS_Content_Comunidades WSS_Content_Comunidades_DPR-OC WSS_Content_Comunidades_MDF WSS_Content_Conservert WSS_Content_Convocatorias_SQLOnly WSS_Content_DocumentosONP WSS_Content_DocumentosTAP WSS_Content_Evaluaciones_SQLOnly WSS_Content_Flujos WSS_Content_Hojavida WSS_Content_IntranetONP WSS_Content_IntranetTmp WSS_Content_MySiteONP WSS_Content_OTI WSS_Content_WorkFlows_SQLOnly WSS_Content_comunidades2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BDPR11G4</t>
+          <t>BDPR11G4 SIGA_1782 SIGA_55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
